--- a/mcp-manual-test-sheet.xlsx
+++ b/mcp-manual-test-sheet.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Call the endpoint with NO credentials. A JSON list of tools means the plugin exposes everything by default: set 'Security hard fail?' to Y on the Scores sheet. A 401/403 is the good outcome. If the plugin is off until enabled, note that.</t>
+          <t>Call the endpoint with NO credentials. A JSON list of tools means the plugin exposes everything by default: set 'Security hard fail?' to Y on the Scores sheet. A 401/403 is the good outcome. If the endpoint is missing or says MCP is disabled, pick 'Disabled' (good safe default) and run this step again after enabling MCP in A4, because the real hard-fail check is whether the ENABLED endpoint answers without credentials.</t>
         </is>
       </c>
       <c r="E20" s="13">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="E21" s="13">
-        <f>"xdg-open '"&amp;$B$7&amp;"/wp-admin/admin.php?page="&amp;$B$4&amp;"' || xdg-open '"&amp;$B$7&amp;"/wp-admin/plugins.php'"</f>
+        <f>"U='"&amp;$B$7&amp;"/wp-admin/admin.php?page="&amp;$B$4&amp;"'; open ""$U"" 2&gt;/dev/null || xdg-open ""$U"""</f>
         <v/>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="E40" s="13">
-        <f>"xdg-open 'https://wordpress.org/support/plugin/"&amp;$B$4&amp;"/'; xdg-open 'https://wordpress.org/plugins/"&amp;$B$4&amp;"/#description'"</f>
+        <f>"for U in 'https://wordpress.org/support/plugin/"&amp;$B$4&amp;"/' 'https://wordpress.org/plugins/"&amp;$B$4&amp;"/#description'; do open ""$U"" 2&gt;/dev/null || xdg-open ""$U""; done"</f>
         <v/>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>A3 Unauth probe (Pass = 401/403)</t>
+          <t>A3 Unauth probe (Pass = 401/403 once enabled)</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -2897,7 +2897,7 @@
       <formula2>5</formula2>
     </dataValidation>
     <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail"</formula1>
+      <formula1>"Pass,Disabled,Fail"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mcp-manual-test-sheet.xlsx
+++ b/mcp-manual-test-sheet.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Call the endpoint with NO credentials. A JSON list of tools means the plugin exposes everything by default: set 'Security hard fail?' to Y on the Scores sheet. A 401/403 is the good outcome. If the endpoint is missing or says MCP is disabled, pick 'Disabled' (good safe default) and run this step again after enabling MCP in A4, because the real hard-fail check is whether the ENABLED endpoint answers without credentials.</t>
+          <t>Call the endpoint with NO credentials. A JSON list of tools means the plugin exposes everything by default: set 'Security hard fail?' to Y on the Scores sheet, UNLESS the source code shows the endpoint is deliberately public (e.g. permission_callback __return_true with a comment explaining it): then pick 'Public by design', leave hard fail at N and note the file:line in Notes. A 401/403 is the good outcome. If the endpoint is missing or says MCP is disabled, pick 'Disabled' (good safe default) and run this step again after enabling MCP in A4, because the real hard-fail check is whether the ENABLED endpoint answers without credentials.</t>
         </is>
       </c>
       <c r="E20" s="13">
@@ -1696,7 +1696,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Slugs!$A$2:$A$37</formula1>
+      <formula1>=Slugs!$A$2:$A$36</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2313,7 +2313,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ylabs-connector-for-wpwriter</t>
+          <t>ylabs-ai-assistant-connector</t>
         </is>
       </c>
       <c r="B21" s="15" t="n"/>
@@ -2341,7 +2341,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ylabs-ai-assistant-connector</t>
+          <t>albert-ai-butler</t>
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
@@ -2369,7 +2369,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>albert-ai-butler</t>
+          <t>acrossai-mcp-manager</t>
         </is>
       </c>
       <c r="B23" s="15" t="n"/>
@@ -2397,7 +2397,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>acrossai-mcp-manager</t>
+          <t>sokket-site-connector-for-mcp</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
@@ -2425,7 +2425,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>sokket-site-connector-for-mcp</t>
+          <t>webo-mcp</t>
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
@@ -2453,7 +2453,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>webo-mcp</t>
+          <t>alphabridge-mcp</t>
         </is>
       </c>
       <c r="B26" s="15" t="n"/>
@@ -2481,7 +2481,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>alphabridge-mcp</t>
+          <t>track-debug</t>
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
@@ -2509,7 +2509,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>track-debug</t>
+          <t>admindra-mcp</t>
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
@@ -2537,7 +2537,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>admindra-mcp</t>
+          <t>devcubic-ai-bridge-for-mcp</t>
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
@@ -2565,7 +2565,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>devcubic-ai-bridge-for-mcp</t>
+          <t>abilities-bridge</t>
         </is>
       </c>
       <c r="B30" s="15" t="n"/>
@@ -2593,7 +2593,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>abilities-bridge</t>
+          <t>strifebridge-mcp</t>
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
@@ -2621,7 +2621,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>strifebridge-mcp</t>
+          <t>bcs-mcp-manager</t>
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
@@ -2649,7 +2649,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>bcs-mcp-manager</t>
+          <t>saddle</t>
         </is>
       </c>
       <c r="B33" s="15" t="n"/>
@@ -2677,7 +2677,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>saddle</t>
+          <t>acadium-agent-publisher</t>
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
@@ -2705,7 +2705,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>acadium-agent-publisher</t>
+          <t>aicom</t>
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
@@ -2733,7 +2733,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>aicom</t>
+          <t>rectus-content-access-for-mcp</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
@@ -2761,7 +2761,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>rectus-content-access-for-mcp</t>
+          <t>mcp-for-woocommerce</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -2789,7 +2789,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>mcp-for-woocommerce</t>
+          <t>counterhand-mcp-for-woocommerce</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>counterhand-mcp-for-woocommerce</t>
+          <t>publishio</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
@@ -2842,36 +2842,8 @@
       <c r="U39" s="15" t="n"/>
       <c r="V39" s="16" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>publishio</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="15" t="n"/>
-      <c r="Q40" s="15" t="n"/>
-      <c r="R40" s="15" t="n"/>
-      <c r="S40" s="15" t="n"/>
-      <c r="T40" s="15" t="n"/>
-      <c r="U40" s="15" t="n"/>
-      <c r="V40" s="16" t="n"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H5:O40">
+  <conditionalFormatting sqref="H5:O39">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -2883,21 +2855,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Partial,Fail"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"App password,API key,OAuth,None,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Disabled,Fail"</formula1>
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Disabled,Public by design,Fail"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2910,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3038,138 +3010,131 @@
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>ylabs-connector-for-wpwriter</t>
+          <t>ylabs-ai-assistant-connector</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>ylabs-ai-assistant-connector</t>
+          <t>albert-ai-butler</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>albert-ai-butler</t>
+          <t>acrossai-mcp-manager</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>acrossai-mcp-manager</t>
+          <t>sokket-site-connector-for-mcp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>sokket-site-connector-for-mcp</t>
+          <t>webo-mcp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>webo-mcp</t>
+          <t>alphabridge-mcp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>alphabridge-mcp</t>
+          <t>track-debug</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>track-debug</t>
+          <t>admindra-mcp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>admindra-mcp</t>
+          <t>devcubic-ai-bridge-for-mcp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>devcubic-ai-bridge-for-mcp</t>
+          <t>abilities-bridge</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>abilities-bridge</t>
+          <t>strifebridge-mcp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>strifebridge-mcp</t>
+          <t>bcs-mcp-manager</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>bcs-mcp-manager</t>
+          <t>saddle</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>saddle</t>
+          <t>acadium-agent-publisher</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>acadium-agent-publisher</t>
+          <t>aicom</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>aicom</t>
+          <t>rectus-content-access-for-mcp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>rectus-content-access-for-mcp</t>
+          <t>mcp-for-woocommerce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>mcp-for-woocommerce</t>
+          <t>counterhand-mcp-for-woocommerce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>counterhand-mcp-for-woocommerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>publishio</t>
         </is>

--- a/mcp-manual-test-sheet.xlsx
+++ b/mcp-manual-test-sheet.xlsx
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="E21" s="13">
-        <f>"U='"&amp;$B$7&amp;"/wp-admin/admin.php?page="&amp;$B$4&amp;"'; open ""$U"" 2&gt;/dev/null || xdg-open ""$U"""</f>
+        <f>"U='"&amp;$B$7&amp;"/wp-admin/admin.php?page="&amp;$B$4&amp;"'; xdg-open ""$U"" 2&gt;/dev/null || open ""$U"""</f>
         <v/>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="E40" s="13">
-        <f>"for U in 'https://wordpress.org/support/plugin/"&amp;$B$4&amp;"/' 'https://wordpress.org/plugins/"&amp;$B$4&amp;"/#description'; do open ""$U"" 2&gt;/dev/null || xdg-open ""$U""; done"</f>
+        <f>"for U in 'https://wordpress.org/support/plugin/"&amp;$B$4&amp;"/' 'https://wordpress.org/plugins/"&amp;$B$4&amp;"/#description'; do xdg-open ""$U"" 2&gt;/dev/null || open ""$U""; done"</f>
         <v/>
       </c>
       <c r="F40" s="12" t="inlineStr">

--- a/mcp-manual-test-sheet.xlsx
+++ b/mcp-manual-test-sheet.xlsx
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Open the plugin's admin page. Does it show a ready-to-copy Claude Desktop config or connector URL? Take a screenshot of the connection instructions and of every security-related setting (read-only, per-tool toggles, roles, confirmations, logging).</t>
+          <t>Open the plugin's admin page. Does it show a ready-to-copy Claude Desktop config or connector URL? Take a screenshot of the connection instructions and of every security-related setting (read-only, per-tool toggles, roles, confirmations, logging). Save screenshots in screenshots/&lt;slug&gt;/ in the repo, named by step (e.g. A4-connection.png).</t>
         </is>
       </c>
       <c r="E21" s="13">
